--- a/data/nzd0526/nzd0526.xlsx
+++ b/data/nzd0526/nzd0526.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S416"/>
+  <dimension ref="A1:S418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26606,6 +26606,132 @@
         <v>309.95</v>
       </c>
       <c r="S416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>351.65</v>
+      </c>
+      <c r="C417" t="n">
+        <v>345.5</v>
+      </c>
+      <c r="D417" t="n">
+        <v>341.35</v>
+      </c>
+      <c r="E417" t="n">
+        <v>341.33</v>
+      </c>
+      <c r="F417" t="n">
+        <v>343.61</v>
+      </c>
+      <c r="G417" t="n">
+        <v>353.39</v>
+      </c>
+      <c r="H417" t="n">
+        <v>352.31</v>
+      </c>
+      <c r="I417" t="n">
+        <v>346.62</v>
+      </c>
+      <c r="J417" t="n">
+        <v>339.43</v>
+      </c>
+      <c r="K417" t="n">
+        <v>326.82</v>
+      </c>
+      <c r="L417" t="n">
+        <v>325.88</v>
+      </c>
+      <c r="M417" t="n">
+        <v>329.66</v>
+      </c>
+      <c r="N417" t="n">
+        <v>330.94</v>
+      </c>
+      <c r="O417" t="n">
+        <v>331.57</v>
+      </c>
+      <c r="P417" t="n">
+        <v>315.7</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>304.34</v>
+      </c>
+      <c r="R417" t="n">
+        <v>311.96</v>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>349.62</v>
+      </c>
+      <c r="C418" t="n">
+        <v>344.21</v>
+      </c>
+      <c r="D418" t="n">
+        <v>340.4</v>
+      </c>
+      <c r="E418" t="n">
+        <v>338.25</v>
+      </c>
+      <c r="F418" t="n">
+        <v>342.05</v>
+      </c>
+      <c r="G418" t="n">
+        <v>352.85</v>
+      </c>
+      <c r="H418" t="n">
+        <v>352.45</v>
+      </c>
+      <c r="I418" t="n">
+        <v>348.35</v>
+      </c>
+      <c r="J418" t="n">
+        <v>340.45</v>
+      </c>
+      <c r="K418" t="n">
+        <v>328.15</v>
+      </c>
+      <c r="L418" t="n">
+        <v>327.28</v>
+      </c>
+      <c r="M418" t="n">
+        <v>331.5</v>
+      </c>
+      <c r="N418" t="n">
+        <v>333.71</v>
+      </c>
+      <c r="O418" t="n">
+        <v>332.95</v>
+      </c>
+      <c r="P418" t="n">
+        <v>318.11</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>306.75</v>
+      </c>
+      <c r="R418" t="n">
+        <v>313.45</v>
+      </c>
+      <c r="S418" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26622,7 +26748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B428"/>
+  <dimension ref="A1:B430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30905,6 +31031,26 @@
       </c>
       <c r="B428" t="n">
         <v>-0.17</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>-0.48</v>
       </c>
     </row>
   </sheetData>
@@ -31073,28 +31219,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.587211488069361</v>
+        <v>4.530600929014938</v>
       </c>
       <c r="J2" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K2" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6212996622080769</v>
+        <v>0.6126049511753339</v>
       </c>
       <c r="M2" t="n">
-        <v>22.6875357296883</v>
+        <v>22.8694466579372</v>
       </c>
       <c r="N2" t="n">
-        <v>709.5325847071649</v>
+        <v>722.4406871616087</v>
       </c>
       <c r="O2" t="n">
-        <v>26.63705285325621</v>
+        <v>26.87825677311698</v>
       </c>
       <c r="P2" t="n">
-        <v>288.568234805802</v>
+        <v>289.1447312443855</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31151,28 +31297,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.835090746882083</v>
+        <v>4.776064043033415</v>
       </c>
       <c r="J3" t="n">
+        <v>417</v>
+      </c>
+      <c r="K3" t="n">
         <v>415</v>
       </c>
-      <c r="K3" t="n">
-        <v>413</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.6780685074104877</v>
+        <v>0.6687806051825014</v>
       </c>
       <c r="M3" t="n">
-        <v>21.08678654940949</v>
+        <v>21.2899732689698</v>
       </c>
       <c r="N3" t="n">
-        <v>610.1483190207105</v>
+        <v>624.8012730013862</v>
       </c>
       <c r="O3" t="n">
-        <v>24.70118051876692</v>
+        <v>24.99602514403812</v>
       </c>
       <c r="P3" t="n">
-        <v>278.3837462545369</v>
+        <v>278.9884850637375</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31229,28 +31375,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.54990395016607</v>
+        <v>4.492674667309832</v>
       </c>
       <c r="J4" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K4" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6715907040477435</v>
+        <v>0.6618266270998447</v>
       </c>
       <c r="M4" t="n">
-        <v>20.14049256266969</v>
+        <v>20.33288201274546</v>
       </c>
       <c r="N4" t="n">
-        <v>560.8732938232514</v>
+        <v>574.8855659000874</v>
       </c>
       <c r="O4" t="n">
-        <v>23.68276364411999</v>
+        <v>23.97677138190393</v>
       </c>
       <c r="P4" t="n">
-        <v>280.4415932750264</v>
+        <v>281.0242992749157</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31307,28 +31453,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.569889693680581</v>
+        <v>4.511353906876621</v>
       </c>
       <c r="J5" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K5" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6809611922994551</v>
+        <v>0.6707040159258268</v>
       </c>
       <c r="M5" t="n">
-        <v>19.83671862425488</v>
+        <v>20.02557218200323</v>
       </c>
       <c r="N5" t="n">
-        <v>542.103391637433</v>
+        <v>556.9877114217717</v>
       </c>
       <c r="O5" t="n">
-        <v>23.28311387330812</v>
+        <v>23.60058709909081</v>
       </c>
       <c r="P5" t="n">
-        <v>280.185095053563</v>
+        <v>280.781108781477</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31385,28 +31531,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.892666921571133</v>
+        <v>4.832192728643943</v>
       </c>
       <c r="J6" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K6" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7173328636568388</v>
+        <v>0.7072400736691935</v>
       </c>
       <c r="M6" t="n">
-        <v>19.30143722003272</v>
+        <v>19.50963680976405</v>
       </c>
       <c r="N6" t="n">
-        <v>522.631319851841</v>
+        <v>538.7776275215225</v>
       </c>
       <c r="O6" t="n">
-        <v>22.86113120236707</v>
+        <v>23.21158390807319</v>
       </c>
       <c r="P6" t="n">
-        <v>276.7402812764761</v>
+        <v>277.3560281041466</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31463,28 +31609,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.610015923815818</v>
+        <v>4.556667753407064</v>
       </c>
       <c r="J7" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K7" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7117362620621263</v>
+        <v>0.7029384073071843</v>
       </c>
       <c r="M7" t="n">
-        <v>18.61300932757439</v>
+        <v>18.78085548743704</v>
       </c>
       <c r="N7" t="n">
-        <v>476.1634050135125</v>
+        <v>488.3609988275876</v>
       </c>
       <c r="O7" t="n">
-        <v>21.82116873619542</v>
+        <v>22.09889134838188</v>
       </c>
       <c r="P7" t="n">
-        <v>287.0698247103355</v>
+        <v>287.6130952413647</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31541,28 +31687,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.820090463018708</v>
+        <v>4.7642883609862</v>
       </c>
       <c r="J8" t="n">
+        <v>417</v>
+      </c>
+      <c r="K8" t="n">
         <v>415</v>
       </c>
-      <c r="K8" t="n">
-        <v>413</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.7213848283551647</v>
+        <v>0.7124463316192721</v>
       </c>
       <c r="M8" t="n">
-        <v>19.01011150556577</v>
+        <v>19.18619457793794</v>
       </c>
       <c r="N8" t="n">
-        <v>498.5235933474371</v>
+        <v>512.0583000908716</v>
       </c>
       <c r="O8" t="n">
-        <v>22.32764191193143</v>
+        <v>22.62870522347383</v>
       </c>
       <c r="P8" t="n">
-        <v>283.3739396988377</v>
+        <v>283.9414002154899</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31619,28 +31765,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9205693676775</v>
+        <v>4.861375953686387</v>
       </c>
       <c r="J9" t="n">
+        <v>417</v>
+      </c>
+      <c r="K9" t="n">
         <v>415</v>
       </c>
-      <c r="K9" t="n">
-        <v>413</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.7300495942638012</v>
+        <v>0.7202969113928763</v>
       </c>
       <c r="M9" t="n">
-        <v>18.81713192875991</v>
+        <v>19.01075641596585</v>
       </c>
       <c r="N9" t="n">
-        <v>497.3932863872653</v>
+        <v>512.9330698935435</v>
       </c>
       <c r="O9" t="n">
-        <v>22.30231571804294</v>
+        <v>22.64802573942249</v>
       </c>
       <c r="P9" t="n">
-        <v>279.3515781670695</v>
+        <v>279.9535217504138</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31697,28 +31843,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.791471485871995</v>
+        <v>4.731503487831171</v>
       </c>
       <c r="J10" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K10" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L10" t="n">
-        <v>0.688599885798291</v>
+        <v>0.6787067989618372</v>
       </c>
       <c r="M10" t="n">
-        <v>20.11525174733408</v>
+        <v>20.31464655699311</v>
       </c>
       <c r="N10" t="n">
-        <v>572.4271513586255</v>
+        <v>587.8662044652508</v>
       </c>
       <c r="O10" t="n">
-        <v>23.92544986742413</v>
+        <v>24.24595233158002</v>
       </c>
       <c r="P10" t="n">
-        <v>275.596105055069</v>
+        <v>276.2094134255151</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31775,28 +31921,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>4.455133617758688</v>
+        <v>4.396684975565982</v>
       </c>
       <c r="J11" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K11" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L11" t="n">
-        <v>0.685931754192022</v>
+        <v>0.6751473333746811</v>
       </c>
       <c r="M11" t="n">
-        <v>19.08961746582196</v>
+        <v>19.27436358778284</v>
       </c>
       <c r="N11" t="n">
-        <v>501.0662786871942</v>
+        <v>515.940247070473</v>
       </c>
       <c r="O11" t="n">
-        <v>22.384509793319</v>
+        <v>22.71431810709872</v>
       </c>
       <c r="P11" t="n">
-        <v>270.4339248547932</v>
+        <v>271.0316935850297</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31853,28 +31999,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.576243393387601</v>
+        <v>4.519622497587172</v>
       </c>
       <c r="J12" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K12" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7133564328953514</v>
+        <v>0.7033189017232224</v>
       </c>
       <c r="M12" t="n">
-        <v>18.07302415506661</v>
+        <v>18.2625766925885</v>
       </c>
       <c r="N12" t="n">
-        <v>464.9161554394411</v>
+        <v>478.9427033803527</v>
       </c>
       <c r="O12" t="n">
-        <v>21.56191446600791</v>
+        <v>21.88475961440638</v>
       </c>
       <c r="P12" t="n">
-        <v>264.4668002484981</v>
+        <v>265.0455287808028</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31931,28 +32077,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.358201241028575</v>
+        <v>4.302712723526772</v>
       </c>
       <c r="J13" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K13" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6954989758095729</v>
+        <v>0.6851318470001951</v>
       </c>
       <c r="M13" t="n">
-        <v>18.16085230125082</v>
+        <v>18.34056585673344</v>
       </c>
       <c r="N13" t="n">
-        <v>461.1946520456188</v>
+        <v>474.6986000468285</v>
       </c>
       <c r="O13" t="n">
-        <v>21.47544299998533</v>
+        <v>21.78757903133867</v>
       </c>
       <c r="P13" t="n">
-        <v>273.1698261002186</v>
+        <v>273.7362233297205</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32009,28 +32155,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>4.1786416296138</v>
+        <v>4.12339223832041</v>
       </c>
       <c r="J14" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K14" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6831539079466491</v>
+        <v>0.6722070876970476</v>
       </c>
       <c r="M14" t="n">
-        <v>17.56781529274576</v>
+        <v>17.76658087621938</v>
       </c>
       <c r="N14" t="n">
-        <v>449.2124489618909</v>
+        <v>462.6651607626692</v>
       </c>
       <c r="O14" t="n">
-        <v>21.19463255076367</v>
+        <v>21.50965273459033</v>
       </c>
       <c r="P14" t="n">
-        <v>279.5525644340672</v>
+        <v>280.1156898175936</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32087,28 +32233,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>3.296162171031626</v>
+        <v>3.245456722790171</v>
       </c>
       <c r="J15" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K15" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6221786863155188</v>
+        <v>0.6090326913798774</v>
       </c>
       <c r="M15" t="n">
-        <v>15.80463725485148</v>
+        <v>15.97307147701787</v>
       </c>
       <c r="N15" t="n">
-        <v>365.1770853658155</v>
+        <v>376.5249712159205</v>
       </c>
       <c r="O15" t="n">
-        <v>19.10960714839045</v>
+        <v>19.40425136963342</v>
       </c>
       <c r="P15" t="n">
-        <v>298.0533864706366</v>
+        <v>298.5700547187703</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32165,28 +32311,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3.121608851266877</v>
+        <v>3.06696963217053</v>
       </c>
       <c r="J16" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K16" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L16" t="n">
-        <v>0.569779661906624</v>
+        <v>0.5546898624705623</v>
       </c>
       <c r="M16" t="n">
-        <v>16.51956077346103</v>
+        <v>16.71613256035714</v>
       </c>
       <c r="N16" t="n">
-        <v>407.2452366351609</v>
+        <v>420.507363046303</v>
       </c>
       <c r="O16" t="n">
-        <v>20.18031805089208</v>
+        <v>20.50627618672642</v>
       </c>
       <c r="P16" t="n">
-        <v>291.3739272697727</v>
+        <v>291.9306768675028</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32243,28 +32389,28 @@
         <v>0.1976</v>
       </c>
       <c r="I17" t="n">
-        <v>2.861832439174465</v>
+        <v>2.806169634035299</v>
       </c>
       <c r="J17" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K17" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5112168035585277</v>
+        <v>0.4951240171688286</v>
       </c>
       <c r="M17" t="n">
-        <v>16.84912244724067</v>
+        <v>17.07558449480394</v>
       </c>
       <c r="N17" t="n">
-        <v>433.4256440214776</v>
+        <v>447.1372583776451</v>
       </c>
       <c r="O17" t="n">
-        <v>20.81887710760303</v>
+        <v>21.14562031196165</v>
       </c>
       <c r="P17" t="n">
-        <v>287.9164507369834</v>
+        <v>288.4836303196739</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32321,28 +32467,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>2.396962061600415</v>
+        <v>2.350595791181694</v>
       </c>
       <c r="J18" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K18" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4635884218957006</v>
+        <v>0.44927841286717</v>
       </c>
       <c r="M18" t="n">
-        <v>15.50827390336026</v>
+        <v>15.68098851849747</v>
       </c>
       <c r="N18" t="n">
-        <v>367.9619696984111</v>
+        <v>377.1505596955141</v>
       </c>
       <c r="O18" t="n">
-        <v>19.18233483438372</v>
+        <v>19.42036456134421</v>
       </c>
       <c r="P18" t="n">
-        <v>297.6809673891468</v>
+        <v>298.1534205696222</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32380,7 +32526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S416"/>
+  <dimension ref="A1:S418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72611,6 +72757,200 @@
         </is>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>-46.299018897027004,169.92348219593927</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>-46.29922479070294,169.9226332924116</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-46.299447247514976,169.92179450525072</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-46.299703908965746,169.92097660692005</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-46.299979618622714,169.9201703411462</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-46.30031654506154,169.9194055748789</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-46.300584113003936,169.91860324609078</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>-46.30083274274317,169.91778214087174</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>-46.301070095934215,169.916949631839</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>-46.30126295705159,169.91608775981624</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-46.30152714436583,169.91528123313475</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>-46.30181611626097,169.91448564820578</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>-46.30208610624179,169.91367305546285</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>-46.3023850066457,169.91287942523783</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>-46.30264671843744,169.9120381129572</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>-46.302937966335634,169.91123669171708</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>-46.30336629854632,169.9105764865033</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>-46.29900208403243,169.92347192839668</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>-46.299214106553386,169.92262676781135</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>-46.29943937932117,169.9217897003795</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-46.29967839938489,169.9209610292256</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-46.29996669815227,169.92016245123887</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-46.30031210954291,169.9194027210586</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-46.30058524463389,169.91860404260296</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-46.30084662054729,169.91779229075726</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>-46.30107827825125,169.91695561609896</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>-46.301273728700444,169.91609526381126</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-46.301538657438066,169.9152885879097</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>-46.301831337858516,169.91449501528803</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>-46.3021087227017,169.91368812740467</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>-46.30239563708046,169.91288866750745</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>-46.30266433557893,169.9120563309328</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>-46.30295560651456,169.91125486330043</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>-46.30337721890929,169.91058769255054</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0526/nzd0526.xlsx
+++ b/data/nzd0526/nzd0526.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S418"/>
+  <dimension ref="A1:S419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26734,6 +26734,69 @@
       <c r="S418" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>345.12</v>
+      </c>
+      <c r="C419" t="n">
+        <v>341.48</v>
+      </c>
+      <c r="D419" t="n">
+        <v>338.62</v>
+      </c>
+      <c r="E419" t="n">
+        <v>335.99</v>
+      </c>
+      <c r="F419" t="n">
+        <v>339.18</v>
+      </c>
+      <c r="G419" t="n">
+        <v>350.26</v>
+      </c>
+      <c r="H419" t="n">
+        <v>350.77</v>
+      </c>
+      <c r="I419" t="n">
+        <v>346.99</v>
+      </c>
+      <c r="J419" t="n">
+        <v>339.36</v>
+      </c>
+      <c r="K419" t="n">
+        <v>327.53</v>
+      </c>
+      <c r="L419" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="M419" t="n">
+        <v>331.65</v>
+      </c>
+      <c r="N419" t="n">
+        <v>336.71</v>
+      </c>
+      <c r="O419" t="n">
+        <v>335.71</v>
+      </c>
+      <c r="P419" t="n">
+        <v>323.07</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>313.52</v>
+      </c>
+      <c r="R419" t="n">
+        <v>316.04</v>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26748,7 +26811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B430"/>
+  <dimension ref="A1:B431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31051,6 +31114,16 @@
       </c>
       <c r="B430" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -31219,28 +31292,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.530600929014938</v>
+        <v>4.500064086322773</v>
       </c>
       <c r="J2" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K2" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6126049511753339</v>
+        <v>0.6075251206643399</v>
       </c>
       <c r="M2" t="n">
-        <v>22.8694466579372</v>
+        <v>22.97092886875895</v>
       </c>
       <c r="N2" t="n">
-        <v>722.4406871616087</v>
+        <v>730.3144718512796</v>
       </c>
       <c r="O2" t="n">
-        <v>26.87825677311698</v>
+        <v>27.0243311083046</v>
       </c>
       <c r="P2" t="n">
-        <v>289.1447312443855</v>
+        <v>289.4564062419109</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31297,28 +31370,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.776064043033415</v>
+        <v>4.745353089729721</v>
       </c>
       <c r="J3" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K3" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6687806051825014</v>
+        <v>0.6637039130158253</v>
       </c>
       <c r="M3" t="n">
-        <v>21.2899732689698</v>
+        <v>21.39676384331029</v>
       </c>
       <c r="N3" t="n">
-        <v>624.8012730013862</v>
+        <v>632.9365351063157</v>
       </c>
       <c r="O3" t="n">
-        <v>24.99602514403812</v>
+        <v>25.15822996767292</v>
       </c>
       <c r="P3" t="n">
-        <v>278.9884850637375</v>
+        <v>279.3038330648014</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31375,28 +31448,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.492674667309832</v>
+        <v>4.463401555180887</v>
       </c>
       <c r="J4" t="n">
+        <v>418</v>
+      </c>
+      <c r="K4" t="n">
         <v>417</v>
       </c>
-      <c r="K4" t="n">
-        <v>416</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6618266270998447</v>
+        <v>0.6566643161339956</v>
       </c>
       <c r="M4" t="n">
-        <v>20.33288201274546</v>
+        <v>20.43310581084436</v>
       </c>
       <c r="N4" t="n">
-        <v>574.8855659000874</v>
+        <v>582.3534224048429</v>
       </c>
       <c r="O4" t="n">
-        <v>23.97677138190393</v>
+        <v>24.13199996694934</v>
       </c>
       <c r="P4" t="n">
-        <v>281.0242992749157</v>
+        <v>281.3230329549076</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31453,28 +31526,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.511353906876621</v>
+        <v>4.480693866839709</v>
       </c>
       <c r="J5" t="n">
+        <v>418</v>
+      </c>
+      <c r="K5" t="n">
         <v>417</v>
       </c>
-      <c r="K5" t="n">
-        <v>416</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6707040159258268</v>
+        <v>0.6650361167372543</v>
       </c>
       <c r="M5" t="n">
-        <v>20.02557218200323</v>
+        <v>20.12578214723407</v>
       </c>
       <c r="N5" t="n">
-        <v>556.9877114217717</v>
+        <v>565.3566195841838</v>
       </c>
       <c r="O5" t="n">
-        <v>23.60058709909081</v>
+        <v>23.77722901399959</v>
       </c>
       <c r="P5" t="n">
-        <v>280.781108781477</v>
+        <v>281.0939961351885</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31531,28 +31604,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.832192728643943</v>
+        <v>4.800647117717242</v>
       </c>
       <c r="J6" t="n">
+        <v>418</v>
+      </c>
+      <c r="K6" t="n">
         <v>417</v>
       </c>
-      <c r="K6" t="n">
-        <v>416</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.7072400736691935</v>
+        <v>0.7016957003805248</v>
       </c>
       <c r="M6" t="n">
-        <v>19.50963680976405</v>
+        <v>19.61978286946652</v>
       </c>
       <c r="N6" t="n">
-        <v>538.7776275215225</v>
+        <v>547.7589083541282</v>
       </c>
       <c r="O6" t="n">
-        <v>23.21158390807319</v>
+        <v>23.40424979259383</v>
       </c>
       <c r="P6" t="n">
-        <v>277.3560281041466</v>
+        <v>277.6779527563058</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31609,28 +31682,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.556667753407064</v>
+        <v>4.529005150998547</v>
       </c>
       <c r="J7" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K7" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7029384073071843</v>
+        <v>0.6981521077249403</v>
       </c>
       <c r="M7" t="n">
-        <v>18.78085548743704</v>
+        <v>18.86919775607108</v>
       </c>
       <c r="N7" t="n">
-        <v>488.3609988275876</v>
+        <v>495.0722781116489</v>
       </c>
       <c r="O7" t="n">
-        <v>22.09889134838188</v>
+        <v>22.25021973176105</v>
       </c>
       <c r="P7" t="n">
-        <v>287.6130952413647</v>
+        <v>287.8954342383637</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31687,28 +31760,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7642883609862</v>
+        <v>4.73601501147956</v>
       </c>
       <c r="J8" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K8" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7124463316192721</v>
+        <v>0.7077973163103561</v>
       </c>
       <c r="M8" t="n">
-        <v>19.18619457793794</v>
+        <v>19.27497990839142</v>
       </c>
       <c r="N8" t="n">
-        <v>512.0583000908716</v>
+        <v>519.1071577982443</v>
       </c>
       <c r="O8" t="n">
-        <v>22.62870522347383</v>
+        <v>22.78392323104703</v>
       </c>
       <c r="P8" t="n">
-        <v>283.9414002154899</v>
+        <v>284.2295727459406</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31765,28 +31838,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.861375953686387</v>
+        <v>4.831974902621582</v>
       </c>
       <c r="J9" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K9" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7202969113928763</v>
+        <v>0.7154197403922319</v>
       </c>
       <c r="M9" t="n">
-        <v>19.01075641596585</v>
+        <v>19.10578904142178</v>
       </c>
       <c r="N9" t="n">
-        <v>512.9330698935435</v>
+        <v>520.653484952059</v>
       </c>
       <c r="O9" t="n">
-        <v>22.64802573942249</v>
+        <v>22.81783260855551</v>
       </c>
       <c r="P9" t="n">
-        <v>279.9535217504138</v>
+        <v>280.2531882360299</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31843,28 +31916,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.731503487831171</v>
+        <v>4.701680681923841</v>
       </c>
       <c r="J10" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K10" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6787067989618372</v>
+        <v>0.6737486385566172</v>
       </c>
       <c r="M10" t="n">
-        <v>20.31464655699311</v>
+        <v>20.41263206837216</v>
       </c>
       <c r="N10" t="n">
-        <v>587.8662044652508</v>
+        <v>595.5607862766049</v>
       </c>
       <c r="O10" t="n">
-        <v>24.24595233158002</v>
+        <v>24.40411412603631</v>
       </c>
       <c r="P10" t="n">
-        <v>276.2094134255151</v>
+        <v>276.5151116422082</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31921,28 +31994,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>4.396684975565982</v>
+        <v>4.367920161762508</v>
       </c>
       <c r="J11" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K11" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6751473333746811</v>
+        <v>0.6698515631567747</v>
       </c>
       <c r="M11" t="n">
-        <v>19.27436358778284</v>
+        <v>19.36353368905112</v>
       </c>
       <c r="N11" t="n">
-        <v>515.940247070473</v>
+        <v>523.1731595811625</v>
       </c>
       <c r="O11" t="n">
-        <v>22.71431810709872</v>
+        <v>22.8729788086546</v>
       </c>
       <c r="P11" t="n">
-        <v>271.0316935850297</v>
+        <v>271.326546869813</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31999,28 +32072,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.519622497587172</v>
+        <v>4.491967018979212</v>
       </c>
       <c r="J12" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K12" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7033189017232224</v>
+        <v>0.698460109211938</v>
       </c>
       <c r="M12" t="n">
-        <v>18.2625766925885</v>
+        <v>18.35307157639882</v>
       </c>
       <c r="N12" t="n">
-        <v>478.9427033803527</v>
+        <v>485.6437851552059</v>
       </c>
       <c r="O12" t="n">
-        <v>21.88475961440638</v>
+        <v>22.03732708735808</v>
       </c>
       <c r="P12" t="n">
-        <v>265.0455287808028</v>
+        <v>265.328843438274</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32077,28 +32150,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.302712723526772</v>
+        <v>4.275895675930091</v>
       </c>
       <c r="J13" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K13" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6851318470001951</v>
+        <v>0.6802151612138592</v>
       </c>
       <c r="M13" t="n">
-        <v>18.34056585673344</v>
+        <v>18.42470423466751</v>
       </c>
       <c r="N13" t="n">
-        <v>474.6986000468285</v>
+        <v>480.9884167722172</v>
       </c>
       <c r="O13" t="n">
-        <v>21.78757903133867</v>
+        <v>21.9314481230086</v>
       </c>
       <c r="P13" t="n">
-        <v>273.7362233297205</v>
+        <v>274.0105867954893</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32155,28 +32228,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>4.12339223832041</v>
+        <v>4.098286566201741</v>
       </c>
       <c r="J14" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K14" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6722070876970476</v>
+        <v>0.6675946870075827</v>
       </c>
       <c r="M14" t="n">
-        <v>17.76658087621938</v>
+        <v>17.85299619280618</v>
       </c>
       <c r="N14" t="n">
-        <v>462.6651607626692</v>
+        <v>468.0745072145262</v>
       </c>
       <c r="O14" t="n">
-        <v>21.50965273459033</v>
+        <v>21.63502963285528</v>
       </c>
       <c r="P14" t="n">
-        <v>280.1156898175936</v>
+        <v>280.3721651448612</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32233,28 +32306,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>3.245456722790171</v>
+        <v>3.222149615142394</v>
       </c>
       <c r="J15" t="n">
+        <v>418</v>
+      </c>
+      <c r="K15" t="n">
         <v>417</v>
       </c>
-      <c r="K15" t="n">
-        <v>416</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.6090326913798774</v>
+        <v>0.6033472102447712</v>
       </c>
       <c r="M15" t="n">
-        <v>15.97307147701787</v>
+        <v>16.04646526021293</v>
       </c>
       <c r="N15" t="n">
-        <v>376.5249712159205</v>
+        <v>381.2238452188524</v>
       </c>
       <c r="O15" t="n">
-        <v>19.40425136963342</v>
+        <v>19.52495442296479</v>
       </c>
       <c r="P15" t="n">
-        <v>298.5700547187703</v>
+        <v>298.8080855572373</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32311,28 +32384,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3.06696963217053</v>
+        <v>3.043044694020315</v>
       </c>
       <c r="J16" t="n">
+        <v>418</v>
+      </c>
+      <c r="K16" t="n">
         <v>417</v>
       </c>
-      <c r="K16" t="n">
-        <v>416</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.5546898624705623</v>
+        <v>0.5486961654498488</v>
       </c>
       <c r="M16" t="n">
-        <v>16.71613256035714</v>
+        <v>16.79830199837237</v>
       </c>
       <c r="N16" t="n">
-        <v>420.507363046303</v>
+        <v>425.401688387267</v>
       </c>
       <c r="O16" t="n">
-        <v>20.50627618672642</v>
+        <v>20.62526820158388</v>
       </c>
       <c r="P16" t="n">
-        <v>291.9306768675028</v>
+        <v>292.1750174855765</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32389,28 +32462,28 @@
         <v>0.1976</v>
       </c>
       <c r="I17" t="n">
-        <v>2.806169634035299</v>
+        <v>2.782621268007659</v>
       </c>
       <c r="J17" t="n">
+        <v>418</v>
+      </c>
+      <c r="K17" t="n">
         <v>417</v>
       </c>
-      <c r="K17" t="n">
-        <v>416</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.4951240171688286</v>
+        <v>0.4890779333389217</v>
       </c>
       <c r="M17" t="n">
-        <v>17.07558449480394</v>
+        <v>17.16432801367245</v>
       </c>
       <c r="N17" t="n">
-        <v>447.1372583776451</v>
+        <v>451.7833704190789</v>
       </c>
       <c r="O17" t="n">
-        <v>21.14562031196165</v>
+        <v>21.25519631570311</v>
       </c>
       <c r="P17" t="n">
-        <v>288.4836303196739</v>
+        <v>288.7241250818209</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32467,28 +32540,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>2.350595791181694</v>
+        <v>2.329387418460787</v>
       </c>
       <c r="J18" t="n">
+        <v>418</v>
+      </c>
+      <c r="K18" t="n">
         <v>417</v>
       </c>
-      <c r="K18" t="n">
-        <v>416</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.44927841286717</v>
+        <v>0.443106286818436</v>
       </c>
       <c r="M18" t="n">
-        <v>15.68098851849747</v>
+        <v>15.7568300585511</v>
       </c>
       <c r="N18" t="n">
-        <v>377.1505596955141</v>
+        <v>380.8845029939325</v>
       </c>
       <c r="O18" t="n">
-        <v>19.42036456134421</v>
+        <v>19.51626252626082</v>
       </c>
       <c r="P18" t="n">
-        <v>298.1534205696222</v>
+        <v>298.3700174471743</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32526,7 +32599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S418"/>
+  <dimension ref="A1:S419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72951,6 +73024,103 @@
         </is>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>-46.298964813844506,169.92344916785598</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>-46.299191495910236,169.92261295994453</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-46.29942463681025,169.9217806975717</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-46.29965968131462,169.9209495988483</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-46.29994292779838,169.92014793584184</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-46.30029083548037,169.91938903329688</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-46.30057166507403,169.91859448445888</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-46.30083571082851,169.91778431165608</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>-46.30106953440264,169.91694922115457</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>-46.30126870733036,169.91609176570796</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>-46.301536930477255,169.9152874846933</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>-46.301832578749604,169.91449577890913</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>-46.30213321706063,169.91370445082097</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>-46.30241689794792,169.91290715205724</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>-46.30270059325595,169.91209382522607</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>-46.30300516003207,169.91130590967725</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>-46.303396201282794,169.91060717152905</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0526/nzd0526.xlsx
+++ b/data/nzd0526/nzd0526.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S419"/>
+  <dimension ref="A1:S420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26797,6 +26797,69 @@
       <c r="S419" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>336.79</v>
+      </c>
+      <c r="C420" t="n">
+        <v>335.79</v>
+      </c>
+      <c r="D420" t="n">
+        <v>333.84</v>
+      </c>
+      <c r="E420" t="n">
+        <v>329.78</v>
+      </c>
+      <c r="F420" t="n">
+        <v>334.05</v>
+      </c>
+      <c r="G420" t="n">
+        <v>344.31</v>
+      </c>
+      <c r="H420" t="n">
+        <v>344.21</v>
+      </c>
+      <c r="I420" t="n">
+        <v>338.72</v>
+      </c>
+      <c r="J420" t="n">
+        <v>330.2</v>
+      </c>
+      <c r="K420" t="n">
+        <v>319.19</v>
+      </c>
+      <c r="L420" t="n">
+        <v>318.63</v>
+      </c>
+      <c r="M420" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="N420" t="n">
+        <v>326.04</v>
+      </c>
+      <c r="O420" t="n">
+        <v>326.43</v>
+      </c>
+      <c r="P420" t="n">
+        <v>314.17</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>306.26</v>
+      </c>
+      <c r="R420" t="n">
+        <v>308.63</v>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26811,7 +26874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B431"/>
+  <dimension ref="A1:B432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31124,6 +31187,16 @@
       </c>
       <c r="B431" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -31292,28 +31365,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.500064086322773</v>
+        <v>4.465109404060144</v>
       </c>
       <c r="J2" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K2" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6075251206643399</v>
+        <v>0.6010957875213584</v>
       </c>
       <c r="M2" t="n">
-        <v>22.97092886875895</v>
+        <v>23.0918309134714</v>
       </c>
       <c r="N2" t="n">
-        <v>730.3144718512796</v>
+        <v>740.9260512134365</v>
       </c>
       <c r="O2" t="n">
-        <v>27.0243311083046</v>
+        <v>27.21995685546611</v>
       </c>
       <c r="P2" t="n">
-        <v>289.4564062419109</v>
+        <v>289.8158952874579</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31370,28 +31443,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.745353089729721</v>
+        <v>4.711457184222351</v>
       </c>
       <c r="J3" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K3" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6637039130158253</v>
+        <v>0.6576744186556287</v>
       </c>
       <c r="M3" t="n">
-        <v>21.39676384331029</v>
+        <v>21.51678028633662</v>
       </c>
       <c r="N3" t="n">
-        <v>632.9365351063157</v>
+        <v>642.9453303123579</v>
       </c>
       <c r="O3" t="n">
-        <v>25.15822996767292</v>
+        <v>25.35636666228736</v>
       </c>
       <c r="P3" t="n">
-        <v>279.3038330648014</v>
+        <v>279.654534602424</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31448,28 +31521,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.463401555180887</v>
+        <v>4.431428003863346</v>
       </c>
       <c r="J4" t="n">
+        <v>419</v>
+      </c>
+      <c r="K4" t="n">
         <v>418</v>
       </c>
-      <c r="K4" t="n">
-        <v>417</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6566643161339956</v>
+        <v>0.6506555585967595</v>
       </c>
       <c r="M4" t="n">
-        <v>20.43310581084436</v>
+        <v>20.54464886618079</v>
       </c>
       <c r="N4" t="n">
-        <v>582.3534224048429</v>
+        <v>591.3235132700387</v>
       </c>
       <c r="O4" t="n">
-        <v>24.13199996694934</v>
+        <v>24.31714443083395</v>
       </c>
       <c r="P4" t="n">
-        <v>281.3230329549076</v>
+        <v>281.6518243528526</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31526,28 +31599,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.480693866839709</v>
+        <v>4.446642655464256</v>
       </c>
       <c r="J5" t="n">
+        <v>419</v>
+      </c>
+      <c r="K5" t="n">
         <v>418</v>
       </c>
-      <c r="K5" t="n">
-        <v>417</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6650361167372543</v>
+        <v>0.6582382040422224</v>
       </c>
       <c r="M5" t="n">
-        <v>20.12578214723407</v>
+        <v>20.24024465724904</v>
       </c>
       <c r="N5" t="n">
-        <v>565.3566195841838</v>
+        <v>575.7579554655448</v>
       </c>
       <c r="O5" t="n">
-        <v>23.77722901399959</v>
+        <v>23.99495687567587</v>
       </c>
       <c r="P5" t="n">
-        <v>281.0939961351885</v>
+        <v>281.4441525903995</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31604,28 +31677,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.800647117717242</v>
+        <v>4.766202972901951</v>
       </c>
       <c r="J6" t="n">
+        <v>419</v>
+      </c>
+      <c r="K6" t="n">
         <v>418</v>
       </c>
-      <c r="K6" t="n">
-        <v>417</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.7016957003805248</v>
+        <v>0.6952397396849542</v>
       </c>
       <c r="M6" t="n">
-        <v>19.61978286946652</v>
+        <v>19.74295846877415</v>
       </c>
       <c r="N6" t="n">
-        <v>547.7589083541282</v>
+        <v>558.4751762293514</v>
       </c>
       <c r="O6" t="n">
-        <v>23.40424979259383</v>
+        <v>23.63207938860547</v>
       </c>
       <c r="P6" t="n">
-        <v>277.6779527563058</v>
+        <v>278.0321498366478</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31682,28 +31755,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.529005150998547</v>
+        <v>4.498072736597528</v>
       </c>
       <c r="J7" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K7" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6981521077249403</v>
+        <v>0.6923077461008793</v>
       </c>
       <c r="M7" t="n">
-        <v>18.86919775607108</v>
+        <v>18.97067142556054</v>
       </c>
       <c r="N7" t="n">
-        <v>495.0722781116489</v>
+        <v>503.565581009608</v>
       </c>
       <c r="O7" t="n">
-        <v>22.25021973176105</v>
+        <v>22.44026695495417</v>
       </c>
       <c r="P7" t="n">
-        <v>287.8954342383637</v>
+        <v>288.213556544438</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31760,28 +31833,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.73601501147956</v>
+        <v>4.70416376423502</v>
       </c>
       <c r="J8" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K8" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7077973163103561</v>
+        <v>0.7020334014642307</v>
       </c>
       <c r="M8" t="n">
-        <v>19.27497990839142</v>
+        <v>19.37815438233444</v>
       </c>
       <c r="N8" t="n">
-        <v>519.1071577982443</v>
+        <v>528.1803354433448</v>
       </c>
       <c r="O8" t="n">
-        <v>22.78392323104703</v>
+        <v>22.9821742975582</v>
       </c>
       <c r="P8" t="n">
-        <v>284.2295727459406</v>
+        <v>284.5567100253118</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31838,28 +31911,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.831974902621582</v>
+        <v>4.798155952606767</v>
       </c>
       <c r="J9" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K9" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7154197403922319</v>
+        <v>0.7091320959073357</v>
       </c>
       <c r="M9" t="n">
-        <v>19.10578904142178</v>
+        <v>19.21943769662334</v>
       </c>
       <c r="N9" t="n">
-        <v>520.653484952059</v>
+        <v>531.0371865482856</v>
       </c>
       <c r="O9" t="n">
-        <v>22.81783260855551</v>
+        <v>23.04424410885038</v>
       </c>
       <c r="P9" t="n">
-        <v>280.2531882360299</v>
+        <v>280.6005353654562</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31916,28 +31989,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.701680681923841</v>
+        <v>4.666989034153356</v>
       </c>
       <c r="J10" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K10" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6737486385566172</v>
+        <v>0.667242652995664</v>
       </c>
       <c r="M10" t="n">
-        <v>20.41263206837216</v>
+        <v>20.53217621455518</v>
       </c>
       <c r="N10" t="n">
-        <v>595.5607862766049</v>
+        <v>606.2345738525638</v>
       </c>
       <c r="O10" t="n">
-        <v>24.40411412603631</v>
+        <v>24.62183124490467</v>
       </c>
       <c r="P10" t="n">
-        <v>276.5151116422082</v>
+        <v>276.873435136059</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31994,28 +32067,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>4.367920161762508</v>
+        <v>4.334712114516099</v>
       </c>
       <c r="J11" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K11" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6698515631567747</v>
+        <v>0.6630137299196999</v>
       </c>
       <c r="M11" t="n">
-        <v>19.36353368905112</v>
+        <v>19.4711971617481</v>
       </c>
       <c r="N11" t="n">
-        <v>523.1731595811625</v>
+        <v>533.0077097455822</v>
       </c>
       <c r="O11" t="n">
-        <v>22.8729788086546</v>
+        <v>23.0869597337021</v>
       </c>
       <c r="P11" t="n">
-        <v>271.326546869813</v>
+        <v>271.6695465333637</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32072,28 +32145,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.491967018979212</v>
+        <v>4.459809815901174</v>
       </c>
       <c r="J12" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K12" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L12" t="n">
-        <v>0.698460109211938</v>
+        <v>0.6920736848124771</v>
       </c>
       <c r="M12" t="n">
-        <v>18.35307157639882</v>
+        <v>18.46271130031963</v>
       </c>
       <c r="N12" t="n">
-        <v>485.6437851552059</v>
+        <v>494.9050825509298</v>
       </c>
       <c r="O12" t="n">
-        <v>22.03732708735808</v>
+        <v>22.24646224798293</v>
       </c>
       <c r="P12" t="n">
-        <v>265.328843438274</v>
+        <v>265.6608028378836</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32150,28 +32223,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.275895675930091</v>
+        <v>4.244746924447258</v>
       </c>
       <c r="J13" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K13" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6802151612138592</v>
+        <v>0.6737777569972356</v>
       </c>
       <c r="M13" t="n">
-        <v>18.42470423466751</v>
+        <v>18.52680747748928</v>
       </c>
       <c r="N13" t="n">
-        <v>480.9884167722172</v>
+        <v>489.6804786030119</v>
       </c>
       <c r="O13" t="n">
-        <v>21.9314481230086</v>
+        <v>22.12872519154712</v>
       </c>
       <c r="P13" t="n">
-        <v>274.0105867954893</v>
+        <v>274.3317289217033</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32228,28 +32301,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>4.098286566201741</v>
+        <v>4.067657426429729</v>
       </c>
       <c r="J14" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K14" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6675946870075827</v>
+        <v>0.6609697569441764</v>
       </c>
       <c r="M14" t="n">
-        <v>17.85299619280618</v>
+        <v>17.96509008834542</v>
       </c>
       <c r="N14" t="n">
-        <v>468.0745072145262</v>
+        <v>476.4838333102331</v>
       </c>
       <c r="O14" t="n">
-        <v>21.63502963285528</v>
+        <v>21.82850964473372</v>
       </c>
       <c r="P14" t="n">
-        <v>280.3721651448612</v>
+        <v>280.6874769690687</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32306,28 +32379,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>3.222149615142394</v>
+        <v>3.194072212453769</v>
       </c>
       <c r="J15" t="n">
+        <v>419</v>
+      </c>
+      <c r="K15" t="n">
         <v>418</v>
       </c>
-      <c r="K15" t="n">
-        <v>417</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.6033472102447712</v>
+        <v>0.5954815351740956</v>
       </c>
       <c r="M15" t="n">
-        <v>16.04646526021293</v>
+        <v>16.14083099929108</v>
       </c>
       <c r="N15" t="n">
-        <v>381.2238452188524</v>
+        <v>388.2944002995594</v>
       </c>
       <c r="O15" t="n">
-        <v>19.52495442296479</v>
+        <v>19.7051871419573</v>
       </c>
       <c r="P15" t="n">
-        <v>298.8080855572373</v>
+        <v>299.0970292168982</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32384,28 +32457,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3.043044694020315</v>
+        <v>3.014545453926488</v>
       </c>
       <c r="J16" t="n">
+        <v>419</v>
+      </c>
+      <c r="K16" t="n">
         <v>418</v>
       </c>
-      <c r="K16" t="n">
-        <v>417</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.5486961654498488</v>
+        <v>0.5406374401884964</v>
       </c>
       <c r="M16" t="n">
-        <v>16.79830199837237</v>
+        <v>16.90172645619187</v>
       </c>
       <c r="N16" t="n">
-        <v>425.401688387267</v>
+        <v>432.6082185051877</v>
       </c>
       <c r="O16" t="n">
-        <v>20.62526820158388</v>
+        <v>20.79923600772845</v>
       </c>
       <c r="P16" t="n">
-        <v>292.1750174855765</v>
+        <v>292.4683022605818</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32462,28 +32535,28 @@
         <v>0.1976</v>
       </c>
       <c r="I17" t="n">
-        <v>2.782621268007659</v>
+        <v>2.755313306497136</v>
       </c>
       <c r="J17" t="n">
+        <v>419</v>
+      </c>
+      <c r="K17" t="n">
         <v>418</v>
       </c>
-      <c r="K17" t="n">
-        <v>417</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.4890779333389217</v>
+        <v>0.4813793810869812</v>
       </c>
       <c r="M17" t="n">
-        <v>17.16432801367245</v>
+        <v>17.27218073528937</v>
       </c>
       <c r="N17" t="n">
-        <v>451.7833704190789</v>
+        <v>458.2536042039494</v>
       </c>
       <c r="O17" t="n">
-        <v>21.25519631570311</v>
+        <v>21.4068588121646</v>
       </c>
       <c r="P17" t="n">
-        <v>288.7241250818209</v>
+        <v>289.0051504467465</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32540,28 +32613,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>2.329387418460787</v>
+        <v>2.304391387318989</v>
       </c>
       <c r="J18" t="n">
+        <v>419</v>
+      </c>
+      <c r="K18" t="n">
         <v>418</v>
       </c>
-      <c r="K18" t="n">
-        <v>417</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.443106286818436</v>
+        <v>0.435084147190377</v>
       </c>
       <c r="M18" t="n">
-        <v>15.7568300585511</v>
+        <v>15.85065823152085</v>
       </c>
       <c r="N18" t="n">
-        <v>380.8845029939325</v>
+        <v>386.2999080043649</v>
       </c>
       <c r="O18" t="n">
-        <v>19.51626252626082</v>
+        <v>19.65451368017954</v>
       </c>
       <c r="P18" t="n">
-        <v>298.3700174471743</v>
+        <v>298.6272508100748</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32599,7 +32672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S419"/>
+  <dimension ref="A1:S420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73121,6 +73194,103 @@
         </is>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>-46.298895822575034,169.92340703564494</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>-46.29914436969328,169.92258418094605</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>-46.29938504736769,169.9217565215155</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-46.2996082480279,169.92091819063796</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-46.29990043932205,169.92012199023208</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-46.30024196262855,169.91935758847788</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-46.300518640119215,169.91855716222605</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-46.30076937010139,169.91773579174694</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>-46.30099605397413,169.9168954802326</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>-46.30120116179454,169.91604471063704</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>-46.30146752309222,169.91524314595503</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>-46.301765156994726,169.91445428887997</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>-46.30204609878131,169.91364639393464</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>-46.30234541212191,169.9128450011631</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>-46.302635534109704,169.91202654719447</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>-46.30295201992237,169.91125116866223</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>-46.3033418926308,169.91055144213178</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0526/nzd0526.xlsx
+++ b/data/nzd0526/nzd0526.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S420"/>
+  <dimension ref="A1:S422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26860,6 +26860,132 @@
       <c r="S420" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>332.6</v>
+      </c>
+      <c r="C421" t="n">
+        <v>332.05</v>
+      </c>
+      <c r="D421" t="n">
+        <v>329.51</v>
+      </c>
+      <c r="E421" t="n">
+        <v>326.07</v>
+      </c>
+      <c r="F421" t="n">
+        <v>330.41</v>
+      </c>
+      <c r="G421" t="n">
+        <v>339.03</v>
+      </c>
+      <c r="H421" t="n">
+        <v>340.26</v>
+      </c>
+      <c r="I421" t="n">
+        <v>336.62</v>
+      </c>
+      <c r="J421" t="n">
+        <v>329.26</v>
+      </c>
+      <c r="K421" t="n">
+        <v>317.54</v>
+      </c>
+      <c r="L421" t="n">
+        <v>317.78</v>
+      </c>
+      <c r="M421" t="n">
+        <v>322.23</v>
+      </c>
+      <c r="N421" t="n">
+        <v>324.75</v>
+      </c>
+      <c r="O421" t="n">
+        <v>326.53</v>
+      </c>
+      <c r="P421" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>309.11</v>
+      </c>
+      <c r="R421" t="n">
+        <v>311.65</v>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>329.68</v>
+      </c>
+      <c r="C422" t="n">
+        <v>330.03</v>
+      </c>
+      <c r="D422" t="n">
+        <v>327.81</v>
+      </c>
+      <c r="E422" t="n">
+        <v>322.95</v>
+      </c>
+      <c r="F422" t="n">
+        <v>326.69</v>
+      </c>
+      <c r="G422" t="n">
+        <v>333.62</v>
+      </c>
+      <c r="H422" t="n">
+        <v>335.24</v>
+      </c>
+      <c r="I422" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="J422" t="n">
+        <v>326.88</v>
+      </c>
+      <c r="K422" t="n">
+        <v>317.86</v>
+      </c>
+      <c r="L422" t="n">
+        <v>318.31</v>
+      </c>
+      <c r="M422" t="n">
+        <v>322.68</v>
+      </c>
+      <c r="N422" t="n">
+        <v>324.69</v>
+      </c>
+      <c r="O422" t="n">
+        <v>326.79</v>
+      </c>
+      <c r="P422" t="n">
+        <v>317.66</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>313.32</v>
+      </c>
+      <c r="R422" t="n">
+        <v>315.39</v>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26874,7 +27000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B432"/>
+  <dimension ref="A1:B434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31197,6 +31323,26 @@
       </c>
       <c r="B432" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -31365,28 +31511,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.465109404060144</v>
+        <v>4.390750522295097</v>
       </c>
       <c r="J2" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K2" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6010957875213584</v>
+        <v>0.5866046541942025</v>
       </c>
       <c r="M2" t="n">
-        <v>23.0918309134714</v>
+        <v>23.35391927743169</v>
       </c>
       <c r="N2" t="n">
-        <v>740.9260512134365</v>
+        <v>765.5837497043187</v>
       </c>
       <c r="O2" t="n">
-        <v>27.21995685546611</v>
+        <v>27.66918411707</v>
       </c>
       <c r="P2" t="n">
-        <v>289.8158952874579</v>
+        <v>290.5827138135508</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31443,28 +31589,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.711457184222351</v>
+        <v>4.640007034319895</v>
       </c>
       <c r="J3" t="n">
+        <v>421</v>
+      </c>
+      <c r="K3" t="n">
         <v>419</v>
       </c>
-      <c r="K3" t="n">
-        <v>417</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.6576744186556287</v>
+        <v>0.644250630494235</v>
       </c>
       <c r="M3" t="n">
-        <v>21.51678028633662</v>
+        <v>21.78190493279929</v>
       </c>
       <c r="N3" t="n">
-        <v>642.9453303123579</v>
+        <v>665.684534606788</v>
       </c>
       <c r="O3" t="n">
-        <v>25.35636666228736</v>
+        <v>25.80086305933947</v>
       </c>
       <c r="P3" t="n">
-        <v>279.654534602424</v>
+        <v>280.3957900354982</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31521,28 +31667,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.431428003863346</v>
+        <v>4.36338550501368</v>
       </c>
       <c r="J4" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K4" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6506555585967595</v>
+        <v>0.6370462799181046</v>
       </c>
       <c r="M4" t="n">
-        <v>20.54464886618079</v>
+        <v>20.78827775073032</v>
       </c>
       <c r="N4" t="n">
-        <v>591.3235132700387</v>
+        <v>612.1558927409137</v>
       </c>
       <c r="O4" t="n">
-        <v>24.31714443083395</v>
+        <v>24.74178434836327</v>
       </c>
       <c r="P4" t="n">
-        <v>281.6518243528526</v>
+        <v>282.353426441897</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31599,28 +31745,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.446642655464256</v>
+        <v>4.374432237979592</v>
       </c>
       <c r="J5" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K5" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6582382040422224</v>
+        <v>0.6429639358247545</v>
       </c>
       <c r="M5" t="n">
-        <v>20.24024465724904</v>
+        <v>20.49084574252904</v>
       </c>
       <c r="N5" t="n">
-        <v>575.7579554655448</v>
+        <v>599.6577580634066</v>
       </c>
       <c r="O5" t="n">
-        <v>23.99495687567587</v>
+        <v>24.4879104470636</v>
       </c>
       <c r="P5" t="n">
-        <v>281.4441525903995</v>
+        <v>282.1887367272759</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31677,28 +31823,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.766202972901951</v>
+        <v>4.692973761260969</v>
       </c>
       <c r="J6" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K6" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6952397396849542</v>
+        <v>0.6806211483546211</v>
       </c>
       <c r="M6" t="n">
-        <v>19.74295846877415</v>
+        <v>20.01398587056754</v>
       </c>
       <c r="N6" t="n">
-        <v>558.4751762293514</v>
+        <v>583.2188670083357</v>
       </c>
       <c r="O6" t="n">
-        <v>23.63207938860547</v>
+        <v>24.14992478266414</v>
       </c>
       <c r="P6" t="n">
-        <v>278.0321498366478</v>
+        <v>278.7872415171922</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31755,28 +31901,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.498072736597528</v>
+        <v>4.429378955895172</v>
       </c>
       <c r="J7" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K7" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6923077461008793</v>
+        <v>0.6779213608386989</v>
       </c>
       <c r="M7" t="n">
-        <v>18.97067142556054</v>
+        <v>19.20263706158735</v>
       </c>
       <c r="N7" t="n">
-        <v>503.565581009608</v>
+        <v>525.2467632973782</v>
       </c>
       <c r="O7" t="n">
-        <v>22.44026695495417</v>
+        <v>22.91826265879196</v>
       </c>
       <c r="P7" t="n">
-        <v>288.213556544438</v>
+        <v>288.9219660107694</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31833,28 +31979,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.70416376423502</v>
+        <v>4.635113288013725</v>
       </c>
       <c r="J8" t="n">
+        <v>421</v>
+      </c>
+      <c r="K8" t="n">
         <v>419</v>
       </c>
-      <c r="K8" t="n">
-        <v>417</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.7020334014642307</v>
+        <v>0.6884590822412298</v>
       </c>
       <c r="M8" t="n">
-        <v>19.37815438233444</v>
+        <v>19.60873314190528</v>
       </c>
       <c r="N8" t="n">
-        <v>528.1803354433448</v>
+        <v>550.1193783831777</v>
       </c>
       <c r="O8" t="n">
-        <v>22.9821742975582</v>
+        <v>23.45462381670569</v>
       </c>
       <c r="P8" t="n">
-        <v>284.5567100253118</v>
+        <v>285.2678662287367</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31911,28 +32057,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.798155952606767</v>
+        <v>4.727839931564521</v>
       </c>
       <c r="J9" t="n">
+        <v>421</v>
+      </c>
+      <c r="K9" t="n">
         <v>419</v>
       </c>
-      <c r="K9" t="n">
-        <v>417</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.7091320959073357</v>
+        <v>0.6954625813544106</v>
       </c>
       <c r="M9" t="n">
-        <v>19.21943769662334</v>
+        <v>19.46032532754979</v>
       </c>
       <c r="N9" t="n">
-        <v>531.0371865482856</v>
+        <v>553.8494112608835</v>
       </c>
       <c r="O9" t="n">
-        <v>23.04424410885038</v>
+        <v>23.53400542323562</v>
       </c>
       <c r="P9" t="n">
-        <v>280.6005353654562</v>
+        <v>281.324717627142</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31989,28 +32135,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.666989034153356</v>
+        <v>4.596506401953089</v>
       </c>
       <c r="J10" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K10" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L10" t="n">
-        <v>0.667242652995664</v>
+        <v>0.6537212204472751</v>
       </c>
       <c r="M10" t="n">
-        <v>20.53217621455518</v>
+        <v>20.77429391477255</v>
       </c>
       <c r="N10" t="n">
-        <v>606.2345738525638</v>
+        <v>628.5152162908407</v>
       </c>
       <c r="O10" t="n">
-        <v>24.62183124490467</v>
+        <v>25.07020574887332</v>
       </c>
       <c r="P10" t="n">
-        <v>276.873435136059</v>
+        <v>277.6034171466963</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32067,28 +32213,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>4.334712114516099</v>
+        <v>4.267784267878858</v>
       </c>
       <c r="J11" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K11" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6630137299196999</v>
+        <v>0.6490238789805438</v>
       </c>
       <c r="M11" t="n">
-        <v>19.4711971617481</v>
+        <v>19.68622156826136</v>
       </c>
       <c r="N11" t="n">
-        <v>533.0077097455822</v>
+        <v>553.1572040571608</v>
       </c>
       <c r="O11" t="n">
-        <v>23.0869597337021</v>
+        <v>23.51929429334904</v>
       </c>
       <c r="P11" t="n">
-        <v>271.6695465333637</v>
+        <v>272.3627007804341</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32145,28 +32291,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.459809815901174</v>
+        <v>4.395809386792369</v>
       </c>
       <c r="J12" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K12" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6920736848124771</v>
+        <v>0.6792955683571645</v>
       </c>
       <c r="M12" t="n">
-        <v>18.46271130031963</v>
+        <v>18.6773105633559</v>
       </c>
       <c r="N12" t="n">
-        <v>494.9050825509298</v>
+        <v>513.3491260322496</v>
       </c>
       <c r="O12" t="n">
-        <v>22.24646224798293</v>
+        <v>22.65720914040936</v>
       </c>
       <c r="P12" t="n">
-        <v>265.6608028378836</v>
+        <v>266.3232728106267</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32223,28 +32369,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.244746924447258</v>
+        <v>4.182297629719513</v>
       </c>
       <c r="J13" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K13" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6737777569972356</v>
+        <v>0.6607250355625224</v>
       </c>
       <c r="M13" t="n">
-        <v>18.52680747748928</v>
+        <v>18.72943515742842</v>
       </c>
       <c r="N13" t="n">
-        <v>489.6804786030119</v>
+        <v>507.280300628581</v>
       </c>
       <c r="O13" t="n">
-        <v>22.12872519154712</v>
+        <v>22.52288393231606</v>
       </c>
       <c r="P13" t="n">
-        <v>274.3317289217033</v>
+        <v>274.9773368476921</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32301,28 +32447,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>4.067657426429729</v>
+        <v>4.005978773773879</v>
       </c>
       <c r="J14" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K14" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6609697569441764</v>
+        <v>0.6474340191680436</v>
       </c>
       <c r="M14" t="n">
-        <v>17.96509008834542</v>
+        <v>18.18814561854577</v>
       </c>
       <c r="N14" t="n">
-        <v>476.4838333102331</v>
+        <v>493.6820247208913</v>
       </c>
       <c r="O14" t="n">
-        <v>21.82850964473372</v>
+        <v>22.2189564273593</v>
       </c>
       <c r="P14" t="n">
-        <v>280.6874769690687</v>
+        <v>281.3241598182573</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32379,28 +32525,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>3.194072212453769</v>
+        <v>3.138942164495764</v>
       </c>
       <c r="J15" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K15" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5954815351740956</v>
+        <v>0.5801779025784088</v>
       </c>
       <c r="M15" t="n">
-        <v>16.14083099929108</v>
+        <v>16.3264196389318</v>
       </c>
       <c r="N15" t="n">
-        <v>388.2944002995594</v>
+        <v>401.9504230853779</v>
       </c>
       <c r="O15" t="n">
-        <v>19.7051871419573</v>
+        <v>20.04870128176331</v>
       </c>
       <c r="P15" t="n">
-        <v>299.0970292168982</v>
+        <v>299.6659073339275</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32457,28 +32603,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3.014545453926488</v>
+        <v>2.960692392183976</v>
       </c>
       <c r="J16" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K16" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5406374401884964</v>
+        <v>0.5259887109805284</v>
       </c>
       <c r="M16" t="n">
-        <v>16.90172645619187</v>
+        <v>17.09247902501622</v>
       </c>
       <c r="N16" t="n">
-        <v>432.6082185051877</v>
+        <v>445.3491105416974</v>
       </c>
       <c r="O16" t="n">
-        <v>20.79923600772845</v>
+        <v>21.10329620087102</v>
       </c>
       <c r="P16" t="n">
-        <v>292.4683022605818</v>
+        <v>293.0239950894751</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32535,28 +32681,28 @@
         <v>0.1976</v>
       </c>
       <c r="I17" t="n">
-        <v>2.755313306497136</v>
+        <v>2.706256773938967</v>
       </c>
       <c r="J17" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K17" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4813793810869812</v>
+        <v>0.4685253545712089</v>
       </c>
       <c r="M17" t="n">
-        <v>17.27218073528937</v>
+        <v>17.45760390866681</v>
       </c>
       <c r="N17" t="n">
-        <v>458.2536042039494</v>
+        <v>468.3701473332486</v>
       </c>
       <c r="O17" t="n">
-        <v>21.4068588121646</v>
+        <v>21.64186099514662</v>
       </c>
       <c r="P17" t="n">
-        <v>289.0051504467465</v>
+        <v>289.5113397304556</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32613,28 +32759,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>2.304391387318989</v>
+        <v>2.259836456512171</v>
       </c>
       <c r="J18" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K18" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L18" t="n">
-        <v>0.435084147190377</v>
+        <v>0.4218365048836968</v>
       </c>
       <c r="M18" t="n">
-        <v>15.85065823152085</v>
+        <v>16.01315692536377</v>
       </c>
       <c r="N18" t="n">
-        <v>386.2999080043649</v>
+        <v>394.6047242339265</v>
       </c>
       <c r="O18" t="n">
-        <v>19.65451368017954</v>
+        <v>19.86466018420467</v>
       </c>
       <c r="P18" t="n">
-        <v>298.6272508100748</v>
+        <v>299.0869907328886</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32672,7 +32818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S420"/>
+  <dimension ref="A1:S422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73291,6 +73437,200 @@
         </is>
       </c>
     </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>-46.29886111987849,169.9233858431309</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>-46.29911339393384,169.92256526472346</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>-46.299349184960846,169.92173462147696</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-46.29957752056958,169.92089942666186</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-46.29987029155013,169.92010358050524</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-46.30019859309985,169.91932968454947</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-46.30048671197808,169.91853468926908</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-46.300752524206466,169.9177234711111</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>-46.300988513404874,169.91688996534242</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>-46.30118779846706,169.9160354011939</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>-46.30146053301114,169.9152386805668</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>-46.30175465078144,169.91444782357144</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>-46.30203556620407,169.91363937488552</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>-46.30234618244348,169.91284567089173</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>-46.30264525643386,169.91203660109255</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>-46.30297288071211,169.91127265789115</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>-46.30336402652438,169.91057415504434</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>-46.29883693565835,169.9233710741388</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>-46.29909666370968,169.92255504794872</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-46.299335105031034,169.92172602331695</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-46.29955167968609,169.92088364672998</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-46.299839481187114,169.9200847661892</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-46.300154155754555,169.91930109363682</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-46.300446134942405,169.9185061287377</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-46.300726132302,169.91770416879635</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>-46.30096942132416,169.91687600211645</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>-46.30119039014274,169.91603720666131</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>-46.3014648915323,169.91524146486756</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>-46.30175837345548,169.9144501144285</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>-46.30203507631674,169.91363904841816</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>-46.30234818527953,169.9128474121862</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>-46.302661046071385,169.91205292923527</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>-46.303003696117536,169.9113044016589</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>-46.30339143736696,169.91060228298105</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0526/nzd0526.xlsx
+++ b/data/nzd0526/nzd0526.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S422"/>
+  <dimension ref="A1:S427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26984,6 +26984,321 @@
         <v>315.39</v>
       </c>
       <c r="S422" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>328.93</v>
+      </c>
+      <c r="C423" t="n">
+        <v>329.21</v>
+      </c>
+      <c r="D423" t="n">
+        <v>326.66</v>
+      </c>
+      <c r="E423" t="n">
+        <v>322.43</v>
+      </c>
+      <c r="F423" t="n">
+        <v>325.48</v>
+      </c>
+      <c r="G423" t="n">
+        <v>332.22</v>
+      </c>
+      <c r="H423" t="n">
+        <v>334.01</v>
+      </c>
+      <c r="I423" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="J423" t="n">
+        <v>327.27</v>
+      </c>
+      <c r="K423" t="n">
+        <v>317.96</v>
+      </c>
+      <c r="L423" t="n">
+        <v>318.31</v>
+      </c>
+      <c r="M423" t="n">
+        <v>323.37</v>
+      </c>
+      <c r="N423" t="n">
+        <v>326.1</v>
+      </c>
+      <c r="O423" t="n">
+        <v>328.13</v>
+      </c>
+      <c r="P423" t="n">
+        <v>319.79</v>
+      </c>
+      <c r="Q423" t="n">
+        <v>315.06</v>
+      </c>
+      <c r="R423" t="n">
+        <v>316.83</v>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>329.08</v>
+      </c>
+      <c r="C424" t="n">
+        <v>328.64</v>
+      </c>
+      <c r="D424" t="n">
+        <v>325.25</v>
+      </c>
+      <c r="E424" t="n">
+        <v>322.44</v>
+      </c>
+      <c r="F424" t="n">
+        <v>324.45</v>
+      </c>
+      <c r="G424" t="n">
+        <v>331.19</v>
+      </c>
+      <c r="H424" t="n">
+        <v>332.88</v>
+      </c>
+      <c r="I424" t="n">
+        <v>331.84</v>
+      </c>
+      <c r="J424" t="n">
+        <v>326.35</v>
+      </c>
+      <c r="K424" t="n">
+        <v>317.74</v>
+      </c>
+      <c r="L424" t="n">
+        <v>317.13</v>
+      </c>
+      <c r="M424" t="n">
+        <v>322.89</v>
+      </c>
+      <c r="N424" t="n">
+        <v>326.58</v>
+      </c>
+      <c r="O424" t="n">
+        <v>328.65</v>
+      </c>
+      <c r="P424" t="n">
+        <v>320.38</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>315.19</v>
+      </c>
+      <c r="R424" t="n">
+        <v>316.41</v>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>329.85</v>
+      </c>
+      <c r="C425" t="n">
+        <v>329.45</v>
+      </c>
+      <c r="D425" t="n">
+        <v>325</v>
+      </c>
+      <c r="E425" t="n">
+        <v>322.95</v>
+      </c>
+      <c r="F425" t="n">
+        <v>324.86</v>
+      </c>
+      <c r="G425" t="n">
+        <v>332.28</v>
+      </c>
+      <c r="H425" t="n">
+        <v>333.95</v>
+      </c>
+      <c r="I425" t="n">
+        <v>332.64</v>
+      </c>
+      <c r="J425" t="n">
+        <v>326.83</v>
+      </c>
+      <c r="K425" t="n">
+        <v>318.51</v>
+      </c>
+      <c r="L425" t="n">
+        <v>318.42</v>
+      </c>
+      <c r="M425" t="n">
+        <v>324.45</v>
+      </c>
+      <c r="N425" t="n">
+        <v>328.07</v>
+      </c>
+      <c r="O425" t="n">
+        <v>329.98</v>
+      </c>
+      <c r="P425" t="n">
+        <v>321.48</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>315.84</v>
+      </c>
+      <c r="R425" t="n">
+        <v>316.86</v>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>328.36</v>
+      </c>
+      <c r="C426" t="n">
+        <v>327.11</v>
+      </c>
+      <c r="D426" t="n">
+        <v>323.13</v>
+      </c>
+      <c r="E426" t="n">
+        <v>321.63</v>
+      </c>
+      <c r="F426" t="n">
+        <v>323.04</v>
+      </c>
+      <c r="G426" t="n">
+        <v>330.34</v>
+      </c>
+      <c r="H426" t="n">
+        <v>332.14</v>
+      </c>
+      <c r="I426" t="n">
+        <v>331.08</v>
+      </c>
+      <c r="J426" t="n">
+        <v>325.37</v>
+      </c>
+      <c r="K426" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="L426" t="n">
+        <v>317.02</v>
+      </c>
+      <c r="M426" t="n">
+        <v>323.47</v>
+      </c>
+      <c r="N426" t="n">
+        <v>327.13</v>
+      </c>
+      <c r="O426" t="n">
+        <v>329.15</v>
+      </c>
+      <c r="P426" t="n">
+        <v>320.3</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>313.4</v>
+      </c>
+      <c r="R426" t="n">
+        <v>314.79</v>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>329.74</v>
+      </c>
+      <c r="C427" t="n">
+        <v>327.7</v>
+      </c>
+      <c r="D427" t="n">
+        <v>323.59</v>
+      </c>
+      <c r="E427" t="n">
+        <v>321.28</v>
+      </c>
+      <c r="F427" t="n">
+        <v>322.89</v>
+      </c>
+      <c r="G427" t="n">
+        <v>330.58</v>
+      </c>
+      <c r="H427" t="n">
+        <v>333.05</v>
+      </c>
+      <c r="I427" t="n">
+        <v>331.91</v>
+      </c>
+      <c r="J427" t="n">
+        <v>326.17</v>
+      </c>
+      <c r="K427" t="n">
+        <v>317.65</v>
+      </c>
+      <c r="L427" t="n">
+        <v>317.4</v>
+      </c>
+      <c r="M427" t="n">
+        <v>323.99</v>
+      </c>
+      <c r="N427" t="n">
+        <v>327.83</v>
+      </c>
+      <c r="O427" t="n">
+        <v>329.99</v>
+      </c>
+      <c r="P427" t="n">
+        <v>319.93</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>312.35</v>
+      </c>
+      <c r="R427" t="n">
+        <v>314.58</v>
+      </c>
+      <c r="S427" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27000,7 +27315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B434"/>
+  <dimension ref="A1:B439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31343,6 +31658,56 @@
       </c>
       <c r="B434" t="n">
         <v>0.37</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -31511,28 +31876,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.390750522295097</v>
+        <v>4.208284249237098</v>
       </c>
       <c r="J2" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K2" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5866046541942025</v>
+        <v>0.550725691229266</v>
       </c>
       <c r="M2" t="n">
-        <v>23.35391927743169</v>
+        <v>23.99064709229962</v>
       </c>
       <c r="N2" t="n">
-        <v>765.5837497043187</v>
+        <v>826.4807400933147</v>
       </c>
       <c r="O2" t="n">
-        <v>27.66918411707</v>
+        <v>28.74857805341535</v>
       </c>
       <c r="P2" t="n">
-        <v>290.5827138135508</v>
+        <v>292.470257784543</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31589,28 +31954,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.640007034319895</v>
+        <v>4.462840243480693</v>
       </c>
       <c r="J3" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K3" t="n">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="L3" t="n">
-        <v>0.644250630494235</v>
+        <v>0.6102087034816572</v>
       </c>
       <c r="M3" t="n">
-        <v>21.78190493279929</v>
+        <v>22.44293424285931</v>
       </c>
       <c r="N3" t="n">
-        <v>665.684534606788</v>
+        <v>723.2067872639793</v>
       </c>
       <c r="O3" t="n">
-        <v>25.80086305933947</v>
+        <v>26.89250429513732</v>
       </c>
       <c r="P3" t="n">
-        <v>280.3957900354982</v>
+        <v>282.2395494862749</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31667,28 +32032,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.36338550501368</v>
+        <v>4.191346972153916</v>
       </c>
       <c r="J4" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K4" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6370462799181046</v>
+        <v>0.6013212345494012</v>
       </c>
       <c r="M4" t="n">
-        <v>20.78827775073032</v>
+        <v>21.42016910960912</v>
       </c>
       <c r="N4" t="n">
-        <v>612.1558927409137</v>
+        <v>667.2451294392353</v>
       </c>
       <c r="O4" t="n">
-        <v>24.74178434836327</v>
+        <v>25.83108842924036</v>
       </c>
       <c r="P4" t="n">
-        <v>282.353426441897</v>
+        <v>284.1329563888265</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31745,28 +32110,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.374432237979592</v>
+        <v>4.196114238347586</v>
       </c>
       <c r="J5" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K5" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6429639358247545</v>
+        <v>0.6046571231499828</v>
       </c>
       <c r="M5" t="n">
-        <v>20.49084574252904</v>
+        <v>21.12281038234457</v>
       </c>
       <c r="N5" t="n">
-        <v>599.6577580634066</v>
+        <v>659.5093701992158</v>
       </c>
       <c r="O5" t="n">
-        <v>24.4879104470636</v>
+        <v>25.68091451251719</v>
       </c>
       <c r="P5" t="n">
-        <v>282.1887367272759</v>
+        <v>284.0332042387371</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31823,28 +32188,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.692973761260969</v>
+        <v>4.507445033431509</v>
       </c>
       <c r="J6" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K6" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6806211483546211</v>
+        <v>0.6420875493415235</v>
       </c>
       <c r="M6" t="n">
-        <v>20.01398587056754</v>
+        <v>20.71698677900379</v>
       </c>
       <c r="N6" t="n">
-        <v>583.2188670083357</v>
+        <v>648.791356694348</v>
       </c>
       <c r="O6" t="n">
-        <v>24.14992478266414</v>
+        <v>25.47138309347076</v>
       </c>
       <c r="P6" t="n">
-        <v>278.7872415171922</v>
+        <v>280.7063050487442</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31901,28 +32266,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.429378955895172</v>
+        <v>4.253312090045934</v>
       </c>
       <c r="J7" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K7" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6779213608386989</v>
+        <v>0.639202398434181</v>
       </c>
       <c r="M7" t="n">
-        <v>19.20263706158735</v>
+        <v>19.79858681329414</v>
       </c>
       <c r="N7" t="n">
-        <v>525.2467632973782</v>
+        <v>584.1523166002894</v>
       </c>
       <c r="O7" t="n">
-        <v>22.91826265879196</v>
+        <v>24.16924319461181</v>
       </c>
       <c r="P7" t="n">
-        <v>288.9219660107694</v>
+        <v>290.7433275864759</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31979,28 +32344,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.635113288013725</v>
+        <v>4.459242105990047</v>
       </c>
       <c r="J8" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K8" t="n">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6884590822412298</v>
+        <v>0.6522576577191945</v>
       </c>
       <c r="M8" t="n">
-        <v>19.60873314190528</v>
+        <v>20.20397621431665</v>
       </c>
       <c r="N8" t="n">
-        <v>550.1193783831777</v>
+        <v>608.9299130221353</v>
       </c>
       <c r="O8" t="n">
-        <v>23.45462381670569</v>
+        <v>24.67650528381471</v>
       </c>
       <c r="P8" t="n">
-        <v>285.2678662287367</v>
+        <v>287.0848661464942</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32057,28 +32422,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.727839931564521</v>
+        <v>4.552554887515913</v>
       </c>
       <c r="J9" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K9" t="n">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6954625813544106</v>
+        <v>0.6603995337126047</v>
       </c>
       <c r="M9" t="n">
-        <v>19.46032532754979</v>
+        <v>20.07730728629055</v>
       </c>
       <c r="N9" t="n">
-        <v>553.8494112608835</v>
+        <v>612.1794078808142</v>
       </c>
       <c r="O9" t="n">
-        <v>23.53400542323562</v>
+        <v>24.74225955487522</v>
       </c>
       <c r="P9" t="n">
-        <v>281.324717627142</v>
+        <v>283.1356594346545</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32135,28 +32500,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.596506401953089</v>
+        <v>4.423872374206275</v>
       </c>
       <c r="J10" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K10" t="n">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6537212204472751</v>
+        <v>0.6201832939996568</v>
       </c>
       <c r="M10" t="n">
-        <v>20.77429391477255</v>
+        <v>21.35686409536497</v>
       </c>
       <c r="N10" t="n">
-        <v>628.5152162908407</v>
+        <v>683.3157131060744</v>
       </c>
       <c r="O10" t="n">
-        <v>25.07020574887332</v>
+        <v>26.14030820602684</v>
       </c>
       <c r="P10" t="n">
-        <v>277.6034171466963</v>
+        <v>279.3969797996891</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32213,28 +32578,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>4.267784267878858</v>
+        <v>4.107642227498562</v>
       </c>
       <c r="J11" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K11" t="n">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6490238789805438</v>
+        <v>0.6157958537463577</v>
       </c>
       <c r="M11" t="n">
-        <v>19.68622156826136</v>
+        <v>20.18373499047927</v>
       </c>
       <c r="N11" t="n">
-        <v>553.1572040571608</v>
+        <v>600.1678619688231</v>
       </c>
       <c r="O11" t="n">
-        <v>23.51929429334904</v>
+        <v>24.4983236562999</v>
       </c>
       <c r="P11" t="n">
-        <v>272.3627007804341</v>
+        <v>274.0264754400025</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32291,28 +32656,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.395809386792369</v>
+        <v>4.241646449750743</v>
       </c>
       <c r="J12" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K12" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6792955683571645</v>
+        <v>0.6485018562625546</v>
       </c>
       <c r="M12" t="n">
-        <v>18.6773105633559</v>
+        <v>19.18119475108253</v>
       </c>
       <c r="N12" t="n">
-        <v>513.3491260322496</v>
+        <v>557.0346227687745</v>
       </c>
       <c r="O12" t="n">
-        <v>22.65720914040936</v>
+        <v>23.60158093791123</v>
       </c>
       <c r="P12" t="n">
-        <v>266.3232728106267</v>
+        <v>267.9240682574485</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32369,28 +32734,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.182297629719513</v>
+        <v>4.035507114356752</v>
       </c>
       <c r="J13" t="n">
+        <v>426</v>
+      </c>
+      <c r="K13" t="n">
         <v>421</v>
       </c>
-      <c r="K13" t="n">
-        <v>416</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.6607250355625224</v>
+        <v>0.6306868571782507</v>
       </c>
       <c r="M13" t="n">
-        <v>18.72943515742842</v>
+        <v>19.18402401681202</v>
       </c>
       <c r="N13" t="n">
-        <v>507.280300628581</v>
+        <v>546.675562482671</v>
       </c>
       <c r="O13" t="n">
-        <v>22.52288393231606</v>
+        <v>23.38109412501201</v>
       </c>
       <c r="P13" t="n">
-        <v>274.9773368476921</v>
+        <v>276.4996974437595</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32447,28 +32812,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>4.005978773773879</v>
+        <v>3.863914888656455</v>
       </c>
       <c r="J14" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K14" t="n">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6474340191680436</v>
+        <v>0.6174449055785198</v>
       </c>
       <c r="M14" t="n">
-        <v>18.18814561854577</v>
+        <v>18.68001251881861</v>
       </c>
       <c r="N14" t="n">
-        <v>493.6820247208913</v>
+        <v>530.4216019455686</v>
       </c>
       <c r="O14" t="n">
-        <v>22.2189564273593</v>
+        <v>23.03088365533482</v>
       </c>
       <c r="P14" t="n">
-        <v>281.3241598182573</v>
+        <v>282.7952615261923</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32525,28 +32890,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>3.138942164495764</v>
+        <v>3.01286829038406</v>
       </c>
       <c r="J15" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K15" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5801779025784088</v>
+        <v>0.5467680625022749</v>
       </c>
       <c r="M15" t="n">
-        <v>16.3264196389318</v>
+        <v>16.74088170632993</v>
       </c>
       <c r="N15" t="n">
-        <v>401.9504230853779</v>
+        <v>430.6336244945545</v>
       </c>
       <c r="O15" t="n">
-        <v>20.04870128176331</v>
+        <v>20.7517137724708</v>
       </c>
       <c r="P15" t="n">
-        <v>299.6659073339275</v>
+        <v>300.9709321719454</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32603,28 +32968,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2.960692392183976</v>
+        <v>2.840649504784152</v>
       </c>
       <c r="J16" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K16" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5259887109805284</v>
+        <v>0.4953942082387552</v>
       </c>
       <c r="M16" t="n">
-        <v>17.09247902501622</v>
+        <v>17.49393142049712</v>
       </c>
       <c r="N16" t="n">
-        <v>445.3491105416974</v>
+        <v>470.3995377538565</v>
       </c>
       <c r="O16" t="n">
-        <v>21.10329620087102</v>
+        <v>21.68869608238025</v>
       </c>
       <c r="P16" t="n">
-        <v>293.0239950894751</v>
+        <v>294.2666042761477</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32681,28 +33046,28 @@
         <v>0.1976</v>
       </c>
       <c r="I17" t="n">
-        <v>2.706256773938967</v>
+        <v>2.596189852402332</v>
       </c>
       <c r="J17" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K17" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4685253545712089</v>
+        <v>0.4413145979933792</v>
       </c>
       <c r="M17" t="n">
-        <v>17.45760390866681</v>
+        <v>17.86003281111221</v>
       </c>
       <c r="N17" t="n">
-        <v>468.3701473332486</v>
+        <v>488.3398932707606</v>
       </c>
       <c r="O17" t="n">
-        <v>21.64186099514662</v>
+        <v>22.09841381798161</v>
       </c>
       <c r="P17" t="n">
-        <v>289.5113397304556</v>
+        <v>290.6507079486592</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32759,28 +33124,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>2.259836456512171</v>
+        <v>2.158763053884726</v>
       </c>
       <c r="J18" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K18" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4218365048836968</v>
+        <v>0.3932889197637314</v>
       </c>
       <c r="M18" t="n">
-        <v>16.01315692536377</v>
+        <v>16.36477821940445</v>
       </c>
       <c r="N18" t="n">
-        <v>394.6047242339265</v>
+        <v>411.4437279501443</v>
       </c>
       <c r="O18" t="n">
-        <v>19.86466018420467</v>
+        <v>20.28407572333884</v>
       </c>
       <c r="P18" t="n">
-        <v>299.0869907328886</v>
+        <v>300.1332591378816</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32818,7 +33183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S422"/>
+  <dimension ref="A1:S427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73631,6 +73996,491 @@
         </is>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>-46.2988307239577,169.9233672807353</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>-46.299089872232315,169.92255090054684</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>-46.29932558037232,169.921720206917</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-46.299547372872,169.92088101674273</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-46.2998294595362,169.92007864648326</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-46.30014265625567,169.91929369488668</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-46.300436192759385,169.91849913084485</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>-46.30071947416152,169.9176992992183</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>-46.30097254985849,169.91687829020742</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>-46.301191200041394,169.9160377708699</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>-46.3014648915323,169.91524146486756</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>-46.30176408155558,169.91445362707663</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>-46.30204658866862,169.9136467204021</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>-46.30235850758801,169.91285638655208</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>-46.30267661640628,169.9120690306073</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>-46.303016432173465,169.91131752142118</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>-46.30340199127258,169.91061311299617</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>-46.29883196629783,169.92336803941595</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>-46.29908515132725,169.92254801759734</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-46.299313902312164,169.9217130755076</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-46.29954745569533,169.9208810673194</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-46.29982092870915,169.92007343714852</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-46.30013419590978,169.91928825152243</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-46.30042705888359,169.91849270188854</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>-46.30071417973641,169.9176954270245</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>-46.30096516972617,169.91687289265985</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>-46.301189418264364,169.916036529611</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>-46.30145518765491,169.91523526585888</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>-46.30176011070335,169.91445118349523</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>-46.302050507767014,169.913649332142</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>-46.302362513259794,169.9128598691427</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>-46.30268092931558,169.91207349061338</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>-46.30301738371782,169.91131850163353</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>-46.30339891305021,169.91060995424135</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>-46.298838343643816,169.92337193397702</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>-46.29909185998181,169.92255211442045</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-46.299311831734066,169.9217118110736</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-46.29955167968609,169.92088364672998</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-46.29982432447527,169.92007551076702</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>-46.30014314909134,169.91929401197592</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-46.30043570777484,169.9184987894843</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>-46.30072059722138,169.91770012059283</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>-46.30096902023002,169.91687570877147</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>-46.3011956544839,169.91604087401754</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>-46.30146579613104,169.91524204274137</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>-46.30177301597298,169.91445912513595</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>-46.30206267330132,169.91365743942032</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>-46.302372758535256,169.91286877654025</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>-46.3026889703325,169.91208180588077</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>-46.30302214143948,169.9113234026959</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>-46.3034022111456,169.91061333862154</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>-46.298826003065116,169.92336439774922</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>-46.299072479423835,169.92254027915627</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-46.2992963438096,169.92170235311025</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-46.29954074700403,169.92087697060927</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-46.29980925058636,169.92006630592581</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-46.300127214070784,169.91928375942695</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-46.30042107740723,169.91848849177669</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>-46.300708083125556,169.91769096813562</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>-46.30095730828059,169.91686714309984</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>-46.30118180521694,169.91603122605116</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>-46.30145428305615,169.9152346879853</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>-46.30176490881647,169.9144541361561</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>-46.30205499840055,169.91365232476113</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>-46.30236636486719,169.91286321778801</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>-46.30268034451433,169.91207288586676</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>-46.30300428168335,169.91130500486622</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>-46.303387039906006,169.91059777047596</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>-46.29883743259439,169.92337137761112</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>-46.29907736597488,169.9225432632606</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>-46.299300153673435,169.9217046796676</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-46.299537848186766,169.92087520042617</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-46.299808008232844,169.92006554728528</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-46.300129185413574,169.91928502778322</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-46.30042843300653,169.9184936690765</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>-46.30071474126636,169.9176958377117</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>-46.30096372578719,169.9168718366181</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>-46.30118868935558,169.91603602182332</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>-46.30145740803367,169.91523668427595</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>-46.301769210573006,169.91445678336973</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>-46.30206071375219,169.91365613354975</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>-46.302372835567404,169.9128688435132</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>-46.3026776398085,169.9120700889138</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>-46.30299659613172,169.91129708777106</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>-46.30338550079464,169.91059619109936</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0526/nzd0526.xlsx
+++ b/data/nzd0526/nzd0526.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S427"/>
+  <dimension ref="A1:S429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27299,6 +27299,132 @@
         <v>314.58</v>
       </c>
       <c r="S427" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>328.47</v>
+      </c>
+      <c r="C428" t="n">
+        <v>325.53</v>
+      </c>
+      <c r="D428" t="n">
+        <v>322.27</v>
+      </c>
+      <c r="E428" t="n">
+        <v>320.15</v>
+      </c>
+      <c r="F428" t="n">
+        <v>321.52</v>
+      </c>
+      <c r="G428" t="n">
+        <v>328.96</v>
+      </c>
+      <c r="H428" t="n">
+        <v>331.45</v>
+      </c>
+      <c r="I428" t="n">
+        <v>329.23</v>
+      </c>
+      <c r="J428" t="n">
+        <v>326.17</v>
+      </c>
+      <c r="K428" t="n">
+        <v>314.71</v>
+      </c>
+      <c r="L428" t="n">
+        <v>314.28</v>
+      </c>
+      <c r="M428" t="n">
+        <v>321.09</v>
+      </c>
+      <c r="N428" t="n">
+        <v>327.83</v>
+      </c>
+      <c r="O428" t="n">
+        <v>326.94</v>
+      </c>
+      <c r="P428" t="n">
+        <v>317.42</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>309.63</v>
+      </c>
+      <c r="R428" t="n">
+        <v>312.27</v>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>327.38</v>
+      </c>
+      <c r="C429" t="n">
+        <v>322.62</v>
+      </c>
+      <c r="D429" t="n">
+        <v>320.3</v>
+      </c>
+      <c r="E429" t="n">
+        <v>317.99</v>
+      </c>
+      <c r="F429" t="n">
+        <v>320.16</v>
+      </c>
+      <c r="G429" t="n">
+        <v>328.7</v>
+      </c>
+      <c r="H429" t="n">
+        <v>330.34</v>
+      </c>
+      <c r="I429" t="n">
+        <v>329.11</v>
+      </c>
+      <c r="J429" t="n">
+        <v>326.61</v>
+      </c>
+      <c r="K429" t="n">
+        <v>313.96</v>
+      </c>
+      <c r="L429" t="n">
+        <v>312.51</v>
+      </c>
+      <c r="M429" t="n">
+        <v>316.76</v>
+      </c>
+      <c r="N429" t="n">
+        <v>327.81</v>
+      </c>
+      <c r="O429" t="n">
+        <v>324.95</v>
+      </c>
+      <c r="P429" t="n">
+        <v>314</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>305.89</v>
+      </c>
+      <c r="R429" t="n">
+        <v>311.84</v>
+      </c>
+      <c r="S429" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27315,7 +27441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B439"/>
+  <dimension ref="A1:B441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31708,6 +31834,26 @@
       </c>
       <c r="B439" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>-1.06</v>
       </c>
     </row>
   </sheetData>
@@ -31876,28 +32022,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.208284249237098</v>
+        <v>4.136863117471833</v>
       </c>
       <c r="J2" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K2" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L2" t="n">
-        <v>0.550725691229266</v>
+        <v>0.536678929324663</v>
       </c>
       <c r="M2" t="n">
-        <v>23.99064709229962</v>
+        <v>24.24025180728493</v>
       </c>
       <c r="N2" t="n">
-        <v>826.4807400933147</v>
+        <v>850.1980982087651</v>
       </c>
       <c r="O2" t="n">
-        <v>28.74857805341535</v>
+        <v>29.15815663255764</v>
       </c>
       <c r="P2" t="n">
-        <v>292.470257784543</v>
+        <v>293.2125694393375</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31954,28 +32100,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.462840243480693</v>
+        <v>4.390553277044086</v>
       </c>
       <c r="J3" t="n">
+        <v>428</v>
+      </c>
+      <c r="K3" t="n">
         <v>426</v>
       </c>
-      <c r="K3" t="n">
-        <v>424</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.6102087034816572</v>
+        <v>0.5957812401047775</v>
       </c>
       <c r="M3" t="n">
-        <v>22.44293424285931</v>
+        <v>22.71722084134601</v>
       </c>
       <c r="N3" t="n">
-        <v>723.2067872639793</v>
+        <v>747.8514544140158</v>
       </c>
       <c r="O3" t="n">
-        <v>26.89250429513732</v>
+        <v>27.34687284524532</v>
       </c>
       <c r="P3" t="n">
-        <v>282.2395494862749</v>
+        <v>282.9953714592127</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32032,28 +32178,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.191346972153916</v>
+        <v>4.121911624239377</v>
       </c>
       <c r="J4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K4" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6013212345494012</v>
+        <v>0.5865067833374014</v>
       </c>
       <c r="M4" t="n">
-        <v>21.42016910960912</v>
+        <v>21.6810652070461</v>
       </c>
       <c r="N4" t="n">
-        <v>667.2451294392353</v>
+        <v>690.2537059260468</v>
       </c>
       <c r="O4" t="n">
-        <v>25.83108842924036</v>
+        <v>26.27267983906565</v>
       </c>
       <c r="P4" t="n">
-        <v>284.1329563888265</v>
+        <v>284.8545733621672</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32110,28 +32256,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.196114238347586</v>
+        <v>4.124612078578309</v>
       </c>
       <c r="J5" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K5" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6046571231499828</v>
+        <v>0.5889820590762547</v>
       </c>
       <c r="M5" t="n">
-        <v>21.12281038234457</v>
+        <v>21.37900016948584</v>
       </c>
       <c r="N5" t="n">
-        <v>659.5093701992158</v>
+        <v>684.1336883453791</v>
       </c>
       <c r="O5" t="n">
-        <v>25.68091451251719</v>
+        <v>26.15594938719256</v>
       </c>
       <c r="P5" t="n">
-        <v>284.0332042387371</v>
+        <v>284.7763011177595</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32188,28 +32334,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.507445033431509</v>
+        <v>4.432940571432844</v>
       </c>
       <c r="J6" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K6" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6420875493415235</v>
+        <v>0.6262448348763185</v>
       </c>
       <c r="M6" t="n">
-        <v>20.71698677900379</v>
+        <v>21.00016660148315</v>
       </c>
       <c r="N6" t="n">
-        <v>648.791356694348</v>
+        <v>675.8384705649087</v>
       </c>
       <c r="O6" t="n">
-        <v>25.47138309347076</v>
+        <v>25.99689347912378</v>
       </c>
       <c r="P6" t="n">
-        <v>280.7063050487442</v>
+        <v>281.4806018271262</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32266,28 +32412,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.253312090045934</v>
+        <v>4.183208120783279</v>
       </c>
       <c r="J7" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K7" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L7" t="n">
-        <v>0.639202398434181</v>
+        <v>0.6235319943404654</v>
       </c>
       <c r="M7" t="n">
-        <v>19.79858681329414</v>
+        <v>20.03557700798144</v>
       </c>
       <c r="N7" t="n">
-        <v>584.1523166002894</v>
+        <v>607.9930223453084</v>
       </c>
       <c r="O7" t="n">
-        <v>24.16924319461181</v>
+        <v>24.65751452083742</v>
       </c>
       <c r="P7" t="n">
-        <v>290.7433275864759</v>
+        <v>291.4719475607338</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32344,28 +32490,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.459242105990047</v>
+        <v>4.38935346778169</v>
       </c>
       <c r="J8" t="n">
+        <v>428</v>
+      </c>
+      <c r="K8" t="n">
         <v>426</v>
       </c>
-      <c r="K8" t="n">
-        <v>424</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.6522576577191945</v>
+        <v>0.6376234250012971</v>
       </c>
       <c r="M8" t="n">
-        <v>20.20397621431665</v>
+        <v>20.4375081500993</v>
       </c>
       <c r="N8" t="n">
-        <v>608.9299130221353</v>
+        <v>632.6309406816018</v>
       </c>
       <c r="O8" t="n">
-        <v>24.67650528381471</v>
+        <v>25.15215578596797</v>
       </c>
       <c r="P8" t="n">
-        <v>287.0848661464942</v>
+        <v>287.8103450812759</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32422,28 +32568,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.552554887515913</v>
+        <v>4.482411605314788</v>
       </c>
       <c r="J9" t="n">
+        <v>428</v>
+      </c>
+      <c r="K9" t="n">
         <v>426</v>
       </c>
-      <c r="K9" t="n">
-        <v>424</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.6603995337126047</v>
+        <v>0.6460269247084522</v>
       </c>
       <c r="M9" t="n">
-        <v>20.07730728629055</v>
+        <v>20.32795940947952</v>
       </c>
       <c r="N9" t="n">
-        <v>612.1794078808142</v>
+        <v>636.0577430889634</v>
       </c>
       <c r="O9" t="n">
-        <v>24.74225955487522</v>
+        <v>25.22018523105973</v>
       </c>
       <c r="P9" t="n">
-        <v>283.1356594346545</v>
+        <v>283.8637794448675</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32500,28 +32646,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.423872374206275</v>
+        <v>4.357361155775983</v>
       </c>
       <c r="J10" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K10" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6201832939996568</v>
+        <v>0.6073642961237122</v>
       </c>
       <c r="M10" t="n">
-        <v>21.35686409536497</v>
+        <v>21.58260499016482</v>
       </c>
       <c r="N10" t="n">
-        <v>683.3157131060744</v>
+        <v>703.8941162147792</v>
       </c>
       <c r="O10" t="n">
-        <v>26.14030820602684</v>
+        <v>26.5310029251587</v>
       </c>
       <c r="P10" t="n">
-        <v>279.3969797996891</v>
+        <v>280.0912476930704</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32578,28 +32724,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>4.107642227498562</v>
+        <v>4.042798211249337</v>
       </c>
       <c r="J11" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K11" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6157958537463577</v>
+        <v>0.6018933780908902</v>
       </c>
       <c r="M11" t="n">
-        <v>20.18373499047927</v>
+        <v>20.38677693410305</v>
       </c>
       <c r="N11" t="n">
-        <v>600.1678619688231</v>
+        <v>619.9599792860605</v>
       </c>
       <c r="O11" t="n">
-        <v>24.4983236562999</v>
+        <v>24.89899554773366</v>
       </c>
       <c r="P11" t="n">
-        <v>274.0264754400025</v>
+        <v>274.7033431629406</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32656,28 +32802,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.241646449750743</v>
+        <v>4.17826847708294</v>
       </c>
       <c r="J12" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K12" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6485018562625546</v>
+        <v>0.6352034637107677</v>
       </c>
       <c r="M12" t="n">
-        <v>19.18119475108253</v>
+        <v>19.39630498562958</v>
       </c>
       <c r="N12" t="n">
-        <v>557.0346227687745</v>
+        <v>576.0767636381908</v>
       </c>
       <c r="O12" t="n">
-        <v>23.60158093791123</v>
+        <v>24.00159918918301</v>
       </c>
       <c r="P12" t="n">
-        <v>267.9240682574485</v>
+        <v>268.5852909393123</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32734,28 +32880,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.035507114356752</v>
+        <v>3.974561463628062</v>
       </c>
       <c r="J13" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K13" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6306868571782507</v>
+        <v>0.6174794023888717</v>
       </c>
       <c r="M13" t="n">
-        <v>19.18402401681202</v>
+        <v>19.37131150226304</v>
       </c>
       <c r="N13" t="n">
-        <v>546.675562482671</v>
+        <v>564.278115707455</v>
       </c>
       <c r="O13" t="n">
-        <v>23.38109412501201</v>
+        <v>23.75453884434415</v>
       </c>
       <c r="P13" t="n">
-        <v>276.4996974437595</v>
+        <v>277.1347895048564</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32812,28 +32958,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>3.863914888656455</v>
+        <v>3.809786341950886</v>
       </c>
       <c r="J14" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K14" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6174449055785198</v>
+        <v>0.6061978109393111</v>
       </c>
       <c r="M14" t="n">
-        <v>18.68001251881861</v>
+        <v>18.86489579739046</v>
       </c>
       <c r="N14" t="n">
-        <v>530.4216019455686</v>
+        <v>543.8426815218962</v>
       </c>
       <c r="O14" t="n">
-        <v>23.03088365533482</v>
+        <v>23.32043484847348</v>
       </c>
       <c r="P14" t="n">
-        <v>282.7952615261923</v>
+        <v>283.3584442347923</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32890,28 +33036,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>3.01286829038406</v>
+        <v>2.961329930579782</v>
       </c>
       <c r="J15" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K15" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5467680625022749</v>
+        <v>0.5326242423695238</v>
       </c>
       <c r="M15" t="n">
-        <v>16.74088170632993</v>
+        <v>16.91043617280252</v>
       </c>
       <c r="N15" t="n">
-        <v>430.6336244945545</v>
+        <v>443.0004502094503</v>
       </c>
       <c r="O15" t="n">
-        <v>20.7517137724708</v>
+        <v>21.04757587489472</v>
       </c>
       <c r="P15" t="n">
-        <v>300.9709321719454</v>
+        <v>301.50695131881</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32968,28 +33114,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2.840649504784152</v>
+        <v>2.790117736077412</v>
       </c>
       <c r="J16" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K16" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4953942082387552</v>
+        <v>0.4817910104459733</v>
       </c>
       <c r="M16" t="n">
-        <v>17.49393142049712</v>
+        <v>17.668517726155</v>
       </c>
       <c r="N16" t="n">
-        <v>470.3995377538565</v>
+        <v>482.0328460973176</v>
       </c>
       <c r="O16" t="n">
-        <v>21.68869608238025</v>
+        <v>21.95524643672481</v>
       </c>
       <c r="P16" t="n">
-        <v>294.2666042761477</v>
+        <v>294.7921578124371</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33046,28 +33192,28 @@
         <v>0.1976</v>
       </c>
       <c r="I17" t="n">
-        <v>2.596189852402332</v>
+        <v>2.547703942831717</v>
       </c>
       <c r="J17" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K17" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4413145979933792</v>
+        <v>0.4282893596134391</v>
       </c>
       <c r="M17" t="n">
-        <v>17.86003281111221</v>
+        <v>18.04652409360373</v>
       </c>
       <c r="N17" t="n">
-        <v>488.3398932707606</v>
+        <v>498.7951605812489</v>
       </c>
       <c r="O17" t="n">
-        <v>22.09841381798161</v>
+        <v>22.33372249718458</v>
       </c>
       <c r="P17" t="n">
-        <v>290.6507079486592</v>
+        <v>291.1549846429754</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33124,28 +33270,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>2.158763053884726</v>
+        <v>2.116326250908567</v>
       </c>
       <c r="J18" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K18" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3932889197637314</v>
+        <v>0.3807973014385828</v>
       </c>
       <c r="M18" t="n">
-        <v>16.36477821940445</v>
+        <v>16.51845122262718</v>
       </c>
       <c r="N18" t="n">
-        <v>411.4437279501443</v>
+        <v>419.2658974434418</v>
       </c>
       <c r="O18" t="n">
-        <v>20.28407572333884</v>
+        <v>20.47598343043483</v>
       </c>
       <c r="P18" t="n">
-        <v>300.1332591378816</v>
+        <v>300.5746157888324</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33183,7 +33329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S427"/>
+  <dimension ref="A1:S429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74481,6 +74627,200 @@
         </is>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>-46.298826914114564,169.92336495411493</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>-46.29905939340546,169.92253228782863</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>-46.29928922102058,169.9216980034604</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-46.29952848914798,169.9208694852649</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-46.299796661403896,169.92005861836986</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-46.30011587884948,169.91927646638018</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-46.30041550008457,169.91848456613266</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>-46.300693242690556,169.91768011426535</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>-46.30096372578719,169.9168718366181</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>-46.30116487833412,169.9160194340987</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>-46.30143175032269,169.91522029368568</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>-46.30174522000702,169.91444202006812</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>-46.30206071375219,169.91365613354975</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>-46.30234934076185,169.91284841677924</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>-46.30265929166732,169.91205111499673</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>-46.30297668689089,169.91127657873466</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>-46.30336857056823,169.91057881796243</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>-46.29881788644266,169.92335944103743</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>-46.299035291939944,169.92251756963353</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>-46.29927290486378,169.92168803973172</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-46.299510599303254,169.92085856071398</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-46.29978539739814,169.92005174003324</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-46.30011374322802,169.9192750923282</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>-46.300406527869576,169.9184782509678</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>-46.300692280067715,169.9176794102307</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>-46.30096725541575,169.9168744180536</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>-46.30115880409363,169.91601520253852</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>-46.301417194504964,169.9152109951843</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>-46.301709399607084,169.91441997695483</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>-46.30206055045644,169.9136560247272</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>-46.30233401136235,169.91283508918173</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>-46.30263429140655,169.91202526211</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>-46.30294931167922,169.9112483788337</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>-46.30336541905396,169.91057558400303</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
